--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_05.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_05.xlsx
@@ -676,7 +676,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -742,7 +742,7 @@
     <t>Izzo</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Kyriakopoulos</t>
@@ -823,7 +823,7 @@
     <t>Elmas</t>
   </si>
   <si>
-    <t xml:space="preserve">Cajuste </t>
+    <t>Cajuste</t>
   </si>
   <si>
     <t>Simeone</t>
@@ -853,7 +853,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Llorente D.</t>
@@ -1270,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O380"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1413,8 +1413,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -2170,8 +2168,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -2927,8 +2923,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -3684,8 +3678,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -4441,8 +4433,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -5198,8 +5188,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -5955,8 +5943,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -6712,8 +6698,6 @@
       <c r="M139" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N139" s="8"/>
-      <c r="O139" s="8"/>
     </row>
     <row r="140">
       <c r="A140" s="11">
@@ -7469,8 +7453,6 @@
       <c r="M158" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N158" s="8"/>
-      <c r="O158" s="8"/>
     </row>
     <row r="159">
       <c r="A159" s="0">
@@ -8226,8 +8208,6 @@
       <c r="M177" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N177" s="8"/>
-      <c r="O177" s="8"/>
     </row>
     <row r="178">
       <c r="A178" s="11">
@@ -8983,8 +8963,6 @@
       <c r="M196" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N196" s="8"/>
-      <c r="O196" s="8"/>
     </row>
     <row r="197">
       <c r="A197" s="0">
@@ -9740,8 +9718,6 @@
       <c r="M215" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N215" s="8"/>
-      <c r="O215" s="8"/>
     </row>
     <row r="216">
       <c r="A216" s="11">
@@ -10497,8 +10473,6 @@
       <c r="M234" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N234" s="8"/>
-      <c r="O234" s="8"/>
     </row>
     <row r="235">
       <c r="A235" s="0">
@@ -11254,8 +11228,6 @@
       <c r="M253" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N253" s="8"/>
-      <c r="O253" s="8"/>
     </row>
     <row r="254">
       <c r="A254" s="11">
@@ -12011,8 +11983,6 @@
       <c r="M272" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N272" s="8"/>
-      <c r="O272" s="8"/>
     </row>
     <row r="273">
       <c r="A273" s="0">
@@ -12645,8 +12615,6 @@
       <c r="M288" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N288" s="8"/>
-      <c r="O288" s="8"/>
     </row>
     <row r="289">
       <c r="A289" s="0">
@@ -13402,8 +13370,6 @@
       <c r="M307" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N307" s="8"/>
-      <c r="O307" s="8"/>
     </row>
     <row r="308">
       <c r="A308" s="11">
@@ -14159,8 +14125,6 @@
       <c r="M326" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N326" s="8"/>
-      <c r="O326" s="8"/>
     </row>
     <row r="327">
       <c r="A327" s="0">
@@ -14875,8 +14839,6 @@
       <c r="M344" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N344" s="8"/>
-      <c r="O344" s="8"/>
     </row>
     <row r="345">
       <c r="A345" s="0">
@@ -15632,8 +15594,6 @@
       <c r="M363" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N363" s="8"/>
-      <c r="O363" s="8"/>
     </row>
     <row r="364">
       <c r="A364" s="11">
@@ -16365,7 +16325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O380"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -16508,8 +16468,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -17265,8 +17223,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -18022,8 +17978,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -18779,8 +18733,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -19536,8 +19488,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -20293,8 +20243,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -21050,8 +20998,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -21807,8 +21753,6 @@
       <c r="M139" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N139" s="8"/>
-      <c r="O139" s="8"/>
     </row>
     <row r="140">
       <c r="A140" s="11">
@@ -22564,8 +22508,6 @@
       <c r="M158" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N158" s="8"/>
-      <c r="O158" s="8"/>
     </row>
     <row r="159">
       <c r="A159" s="0">
@@ -23321,8 +23263,6 @@
       <c r="M177" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N177" s="8"/>
-      <c r="O177" s="8"/>
     </row>
     <row r="178">
       <c r="A178" s="11">
@@ -24078,8 +24018,6 @@
       <c r="M196" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N196" s="8"/>
-      <c r="O196" s="8"/>
     </row>
     <row r="197">
       <c r="A197" s="0">
@@ -24835,8 +24773,6 @@
       <c r="M215" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N215" s="8"/>
-      <c r="O215" s="8"/>
     </row>
     <row r="216">
       <c r="A216" s="11">
@@ -25592,8 +25528,6 @@
       <c r="M234" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N234" s="8"/>
-      <c r="O234" s="8"/>
     </row>
     <row r="235">
       <c r="A235" s="0">
@@ -26349,8 +26283,6 @@
       <c r="M253" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N253" s="8"/>
-      <c r="O253" s="8"/>
     </row>
     <row r="254">
       <c r="A254" s="11">
@@ -27106,8 +27038,6 @@
       <c r="M272" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N272" s="8"/>
-      <c r="O272" s="8"/>
     </row>
     <row r="273">
       <c r="A273" s="0">
@@ -27740,8 +27670,6 @@
       <c r="M288" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N288" s="8"/>
-      <c r="O288" s="8"/>
     </row>
     <row r="289">
       <c r="A289" s="0">
@@ -28497,8 +28425,6 @@
       <c r="M307" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N307" s="8"/>
-      <c r="O307" s="8"/>
     </row>
     <row r="308">
       <c r="A308" s="11">
@@ -29254,8 +29180,6 @@
       <c r="M326" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N326" s="8"/>
-      <c r="O326" s="8"/>
     </row>
     <row r="327">
       <c r="A327" s="0">
@@ -29970,8 +29894,6 @@
       <c r="M344" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N344" s="8"/>
-      <c r="O344" s="8"/>
     </row>
     <row r="345">
       <c r="A345" s="0">
@@ -30727,8 +30649,6 @@
       <c r="M363" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N363" s="8"/>
-      <c r="O363" s="8"/>
     </row>
     <row r="364">
       <c r="A364" s="11">
@@ -31460,7 +31380,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="xr">
-  <dimension ref="A1:O380"/>
+  <dimension ref="A1:M380"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -31603,8 +31523,6 @@
       <c r="M6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="0">
@@ -32360,8 +32278,6 @@
       <c r="M25" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="11">
@@ -33117,8 +33033,6 @@
       <c r="M44" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N44" s="8"/>
-      <c r="O44" s="8"/>
     </row>
     <row r="45">
       <c r="A45" s="0">
@@ -33874,8 +33788,6 @@
       <c r="M63" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N63" s="8"/>
-      <c r="O63" s="8"/>
     </row>
     <row r="64">
       <c r="A64" s="11">
@@ -34631,8 +34543,6 @@
       <c r="M82" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N82" s="8"/>
-      <c r="O82" s="8"/>
     </row>
     <row r="83">
       <c r="A83" s="0">
@@ -35388,8 +35298,6 @@
       <c r="M101" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N101" s="8"/>
-      <c r="O101" s="8"/>
     </row>
     <row r="102">
       <c r="A102" s="11">
@@ -36145,8 +36053,6 @@
       <c r="M120" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N120" s="8"/>
-      <c r="O120" s="8"/>
     </row>
     <row r="121">
       <c r="A121" s="0">
@@ -36902,8 +36808,6 @@
       <c r="M139" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N139" s="8"/>
-      <c r="O139" s="8"/>
     </row>
     <row r="140">
       <c r="A140" s="11">
@@ -37659,8 +37563,6 @@
       <c r="M158" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N158" s="8"/>
-      <c r="O158" s="8"/>
     </row>
     <row r="159">
       <c r="A159" s="0">
@@ -38416,8 +38318,6 @@
       <c r="M177" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N177" s="8"/>
-      <c r="O177" s="8"/>
     </row>
     <row r="178">
       <c r="A178" s="11">
@@ -39173,8 +39073,6 @@
       <c r="M196" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N196" s="8"/>
-      <c r="O196" s="8"/>
     </row>
     <row r="197">
       <c r="A197" s="0">
@@ -39930,8 +39828,6 @@
       <c r="M215" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N215" s="8"/>
-      <c r="O215" s="8"/>
     </row>
     <row r="216">
       <c r="A216" s="11">
@@ -40687,8 +40583,6 @@
       <c r="M234" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N234" s="8"/>
-      <c r="O234" s="8"/>
     </row>
     <row r="235">
       <c r="A235" s="0">
@@ -41444,8 +41338,6 @@
       <c r="M253" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N253" s="8"/>
-      <c r="O253" s="8"/>
     </row>
     <row r="254">
       <c r="A254" s="11">
@@ -42201,8 +42093,6 @@
       <c r="M272" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N272" s="8"/>
-      <c r="O272" s="8"/>
     </row>
     <row r="273">
       <c r="A273" s="0">
@@ -42835,8 +42725,6 @@
       <c r="M288" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N288" s="8"/>
-      <c r="O288" s="8"/>
     </row>
     <row r="289">
       <c r="A289" s="0">
@@ -43592,8 +43480,6 @@
       <c r="M307" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N307" s="8"/>
-      <c r="O307" s="8"/>
     </row>
     <row r="308">
       <c r="A308" s="11">
@@ -44349,8 +44235,6 @@
       <c r="M326" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N326" s="8"/>
-      <c r="O326" s="8"/>
     </row>
     <row r="327">
       <c r="A327" s="0">
@@ -45065,8 +44949,6 @@
       <c r="M344" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N344" s="8"/>
-      <c r="O344" s="8"/>
     </row>
     <row r="345">
       <c r="A345" s="0">
@@ -45822,8 +45704,6 @@
       <c r="M363" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="N363" s="8"/>
-      <c r="O363" s="8"/>
     </row>
     <row r="364">
       <c r="A364" s="11">
